--- a/data/trans_dic/IP31KM04_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM04_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,1; 51,1</t>
+          <t>38,96; 61,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,5; 62,38</t>
+          <t>37,18; 52,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,38; 56,1</t>
+          <t>40,41; 52,73</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,0; 54,49</t>
+          <t>49,0; 61,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,68; 60,6</t>
+          <t>42,95; 55,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,49; 55,94</t>
+          <t>48,06; 57,1</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,21; 40,8</t>
+          <t>24,85; 38,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,15; 39,27</t>
+          <t>29,22; 42,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,53; 37,65</t>
+          <t>29,01; 38,85</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,82; 54,54</t>
+          <t>42,39; 55,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,11; 55,56</t>
+          <t>41,85; 55,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,75; 53,0</t>
+          <t>43,61; 52,8</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,04; 46,6</t>
+          <t>43,48; 50,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,44; 50,23</t>
+          <t>41,2; 48,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,45; 47,45</t>
+          <t>43,27; 48,28</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>58686</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69037</t>
+          <t>52539</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119448</t>
+          <t>111225</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41242; 58379</t>
+          <t>47879; 75507</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54045; 85342</t>
+          <t>44094; 62177</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103887; 140848</t>
+          <t>97585; 127334</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>88303</t>
+          <t>128123</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>133861</t>
+          <t>89266</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>222165</t>
+          <t>217388</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76316; 101418</t>
+          <t>113316; 142965</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118009; 149993</t>
+          <t>77572; 100897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>201603; 242574</t>
+          <t>197919; 235174</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60553</t>
+          <t>52489</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57694</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118247</t>
+          <t>107970</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36157; 76797</t>
+          <t>41376; 64055</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46045; 71894</t>
+          <t>45309; 66069</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91104; 139807</t>
+          <t>93286; 124936</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>113</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>78796</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>85922</t>
+          <t>79305</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164718</t>
+          <t>160305</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68796; 89735</t>
+          <t>70434; 91899</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74659; 98508</t>
+          <t>68628; 91065</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149547; 181182</t>
+          <t>143969; 174327</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>408</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>278064</t>
+          <t>320299</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>346514</t>
+          <t>276591</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>624578</t>
+          <t>596889</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>241923; 304384</t>
+          <t>298651; 346673</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316080; 374094</t>
+          <t>254684; 298384</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>579463; 663286</t>
+          <t>564640; 630113</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM04_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM04_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>47,75%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>38,96; 61,44</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37,18; 52,43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40,41; 52,73</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>55,41%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>49,43%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>52,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>49,0; 61,83</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>42,95; 55,87</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>48,06; 57,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>31,52%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>24,85; 38,47</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>29,22; 42,61</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>29,01; 38,85</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>48,75%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>42,39; 55,31</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41,85; 55,53</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43,61; 52,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>46,63%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>44,74%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>45,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>43,48; 50,47</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41,2; 48,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43,27; 48,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4775264230711368</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4430010124900262</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4605709990579541</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>58686</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52539</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>111225</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.3895878478803373</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3717902981186587</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4040868743818052</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>47879; 75507</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>44094; 62177</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>97585; 127334</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6143995129802041</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5242627048759513</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5272755157339519</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5540661350040381</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.494292148598045</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5278546774008352</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>128123</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>89266</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>217388</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4900327031745606</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4295425948986349</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4805798739162311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>113316; 142965</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>77572; 100897</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>197919; 235174</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.618250759848993</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5586959016420022</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5710419036226659</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3152083703015851</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3578553638273287</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3357703574285768</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>52489</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>55481</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>107970</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.2484686773071321</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.2922448461867661</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.2901048720337135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>41376; 64055</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>45309; 66069</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>93286; 124936</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3846613863504338</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4261464482877962</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3885318851679747</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4874703896202747</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4836274240036248</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4855616294836301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>81001</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>79305</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>160305</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4238821944855995</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4185150968710184</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4360793867161555</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>70434; 91899</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>68628; 91065</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>143969; 174327</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5530614213927229</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.555345774630116</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.528032989408345</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.4663473195374052</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4474070725283274</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.4573751166400384</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>320299</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>276591</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>596889</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.4348287894640795</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4119714322322891</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.4326639482468276</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>298651; 346673</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>254684; 298384</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>564640; 630113</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.5047485719750419</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4826592264567426</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.482833925059578</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>58686</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>52539</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>111225</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>47879</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>44094</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>97585</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>75507</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>62177</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>127334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>128123</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>89266</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>217388</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>113316</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>77572</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>197919</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>142965</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>100897</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>235174</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>52489</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>55481</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>107970</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>41376</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>45309</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>93286</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>64055</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>66069</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>124936</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>81001</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>79305</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>160305</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>70434</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>68628</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>143969</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>91899</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>91065</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>174327</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>437</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>408</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>320299</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>276591</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>596889</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>298651</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>254684</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>564640</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>346673</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>298384</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>630113</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>